--- a/excel/Raspored_odvoza_Zona1_2026.xlsx
+++ b/excel/Raspored_odvoza_Zona1_2026.xlsx
@@ -1116,7 +1116,7 @@
     <row r="30">
       <c r="A30" s="21" t="inlineStr">
         <is>
-          <t>• Spremnike iznijeti na javnu površinu najkasnije do 07:00. Info: 0800 200 214, info@gos.hr, www.gos.hr</t>
+          <t>• Spremnike iznijeti na javnu površinu najkasnije do 07:00.</t>
         </is>
       </c>
     </row>
@@ -1161,7 +1161,7 @@
     <row r="2">
       <c r="A2" s="22" t="inlineStr">
         <is>
-          <t>Izvor: GOS d.o.o., RASPORED_2026_Zona_1.pdf. "x" = odvoz tog dana. Spremnike iznijeti do 07:00. Prošli datumi su posivljeni.</t>
+          <t>"x" = odvoz tog dana. Spremnike iznijeti do 07:00. Prošli datumi su posivljeni.</t>
         </is>
       </c>
     </row>
